--- a/膜料庫存.xlsx
+++ b/膜料庫存.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office ÃÂ¤ÃÂ½ÃÂÃÂ¦ÃÂÃÂ¯ÃÂ¤ÃÂ¸ÃÂ»ÃÂ©ÃÂ¡ÃÂ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office ÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂ¯ÃÂÃÂ¤ÃÂÃÂ¸ÃÂÃÂ»ÃÂÃÂ©ÃÂÃÂ¡ÃÂÃÂ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -134,10 +134,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¦ÃÂ¸ÃÂ¸ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ§ÃÂ­ÃÂÃÂ§ÃÂºÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂ¦ÃÂÃÂ¸ÃÂÃÂ¸ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ§ÃÂÃÂ­ÃÂÃÂÃÂÃÂ§ÃÂÃÂºÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -186,10 +186,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¦ÃÂ¸ÃÂ¸ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ§ÃÂ­ÃÂÃÂ§ÃÂºÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂ¦ÃÂÃÂ¸ÃÂÃÂ¸ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ§ÃÂÃÂ­ÃÂÃÂÃÂÃÂ§ÃÂÃÂºÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -16907,7 +16907,7 @@
         <v>ax 啞液態金屬銀</v>
       </c>
       <c r="S4" s="3" t="str">
-        <v>全新</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
